--- a/data/Data Inflasi.xlsx
+++ b/data/Data Inflasi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\jaktimstats_flutter\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\jaktimstats-data-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E8034C-8FAE-4661-A2FF-F721CFD9E45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC4A78F-E7FE-4BBF-B17A-2EB5333976B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{20580D1D-BE1B-4647-B826-3932A4BF3763}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
   <si>
     <t>DATA STRATEGIS KOTA JAKARTA TIMUR 2010 - 2025</t>
   </si>
@@ -54,375 +54,47 @@
     <t>Persen</t>
   </si>
   <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>0.47</t>
-  </si>
-  <si>
-    <t>0.48</t>
-  </si>
-  <si>
-    <t>0.88</t>
-  </si>
-  <si>
-    <t>(0.41)</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>0.99</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>0.14</t>
-  </si>
-  <si>
-    <t>0.46</t>
-  </si>
-  <si>
-    <t>0.09</t>
-  </si>
-  <si>
-    <t>(0.19)</t>
-  </si>
-  <si>
     <t>Februari</t>
-  </si>
-  <si>
-    <t>0.21</t>
-  </si>
-  <si>
-    <t>0.17</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>(0.06)</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>0.37</t>
-  </si>
-  <si>
-    <t>0.26</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>0.18</t>
-  </si>
-  <si>
-    <t>(0.05)</t>
-  </si>
-  <si>
-    <t>0.19</t>
-  </si>
-  <si>
-    <t>0.45</t>
   </si>
   <si>
     <t>Maret</t>
   </si>
   <si>
-    <t>0.07</t>
-  </si>
-  <si>
-    <t>-0.01</t>
-  </si>
-  <si>
-    <t>0.42</t>
-  </si>
-  <si>
-    <t>0.15</t>
-  </si>
-  <si>
-    <t>0.05</t>
-  </si>
-  <si>
-    <t>0.06</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
     <t>April</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>0.13</t>
-  </si>
-  <si>
-    <t>(0.24)</t>
-  </si>
-  <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>(0.27)</t>
-  </si>
-  <si>
-    <t>(0.02)</t>
-  </si>
-  <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>0.29</t>
-  </si>
-  <si>
-    <t>0.08</t>
-  </si>
-  <si>
-    <t>0.70</t>
   </si>
   <si>
     <t>Mei</t>
   </si>
   <si>
-    <t>0.12</t>
-  </si>
-  <si>
-    <t>(0.07)</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>0.59</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>(0.10)</t>
-  </si>
-  <si>
     <t>Juni</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>0.38</t>
-  </si>
-  <si>
-    <t>0.93</t>
-  </si>
-  <si>
-    <t>0.35</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>0.01</t>
   </si>
   <si>
     <t>Juli</t>
   </si>
   <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>0.55</t>
-  </si>
-  <si>
-    <t>3.16</t>
-  </si>
-  <si>
-    <t>1.17</t>
-  </si>
-  <si>
-    <t>0.97</t>
-  </si>
-  <si>
-    <t>0.64</t>
-  </si>
-  <si>
-    <t>(0.04)</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
     <t>Agustus</t>
-  </si>
-  <si>
-    <t>1.15</t>
-  </si>
-  <si>
-    <t>0.81</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>0.03</t>
-  </si>
-  <si>
-    <t>(0.11)</t>
   </si>
   <si>
     <t>September</t>
   </si>
   <si>
-    <t>0.39</t>
-  </si>
-  <si>
-    <t>0.16</t>
-  </si>
-  <si>
-    <t>(0.13)</t>
-  </si>
-  <si>
-    <t>0.02</t>
-  </si>
-  <si>
-    <t>1.21</t>
-  </si>
-  <si>
     <t>Oktober</t>
-  </si>
-  <si>
-    <t>-0.26</t>
-  </si>
-  <si>
-    <t>0.53</t>
-  </si>
-  <si>
-    <t>(0.03)</t>
-  </si>
-  <si>
-    <t>0.28</t>
   </si>
   <si>
     <t>November</t>
   </si>
   <si>
-    <t>1.43</t>
-  </si>
-  <si>
-    <t>0.30</t>
-  </si>
-  <si>
     <t>Desember</t>
   </si>
   <si>
-    <t>0.76</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
-    <t>2.74</t>
-  </si>
-  <si>
-    <t>0.60</t>
-  </si>
-  <si>
     <t>Tahunan (inflasi tahun kalender, bulan t terhadap Desember 2020)</t>
-  </si>
-  <si>
-    <t>6.21</t>
-  </si>
-  <si>
-    <t>3.97</t>
-  </si>
-  <si>
-    <t>4.52</t>
-  </si>
-  <si>
-    <t>8.00</t>
-  </si>
-  <si>
-    <t>8.95</t>
-  </si>
-  <si>
-    <t>3.30</t>
-  </si>
-  <si>
-    <t>2.37</t>
-  </si>
-  <si>
-    <t>3.72</t>
-  </si>
-  <si>
-    <t>3.27</t>
-  </si>
-  <si>
-    <t>3.23</t>
-  </si>
-  <si>
-    <t>1.59</t>
-  </si>
-  <si>
-    <t>1.53</t>
-  </si>
-  <si>
-    <t>4.21</t>
-  </si>
-  <si>
-    <t>2.28</t>
-  </si>
-  <si>
-    <t>1.48</t>
-  </si>
-  <si>
-    <t>2.00</t>
-  </si>
-  <si>
-    <t>1.44</t>
-  </si>
-  <si>
-    <t>0.11</t>
-  </si>
-  <si>
-    <t>0.31</t>
-  </si>
-  <si>
-    <t>2.63</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd\.mm"/>
-    <numFmt numFmtId="165" formatCode="d\.m"/>
-  </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -452,8 +124,20 @@
       <color rgb="FFFF0000"/>
       <name val="Tahoma"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -474,20 +158,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCFF33"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor rgb="FFCCFF33"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD8D8D8"/>
-        <bgColor rgb="FFD8D8D8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -523,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -540,54 +218,49 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -909,26 +582,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -1128,27 +801,27 @@
       <c r="AA5" s="1"/>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="14"/>
+      <c r="B6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="10"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="15"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -1159,849 +832,849 @@
       <c r="AA6" s="1"/>
     </row>
     <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="16">
+        <v>0.72</v>
+      </c>
+      <c r="E7" s="16">
+        <v>0.47</v>
+      </c>
+      <c r="F7" s="16">
+        <v>0.48</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="H7" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="17">
+        <v>-0.41</v>
+      </c>
+      <c r="J7" s="16">
+        <v>0.24</v>
+      </c>
+      <c r="K7" s="16">
+        <v>0.99</v>
+      </c>
+      <c r="L7" s="16">
+        <v>0.43</v>
+      </c>
+      <c r="M7" s="16">
+        <v>0.24</v>
+      </c>
+      <c r="N7" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="O7" s="16">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P7" s="16">
+        <v>0.46</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>0.09</v>
+      </c>
+      <c r="R7" s="17">
+        <v>-0.19</v>
+      </c>
+      <c r="S7" s="22">
+        <v>-0.5</v>
+      </c>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+      <c r="W7" s="11"/>
+      <c r="X7" s="11"/>
+      <c r="Y7" s="11"/>
+      <c r="Z7" s="11"/>
+      <c r="AA7" s="11"/>
+    </row>
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="C8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="16">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E8" s="16">
+        <v>0.21</v>
+      </c>
+      <c r="F8" s="16">
+        <v>0.17</v>
+      </c>
+      <c r="G8" s="16">
+        <v>0.65</v>
+      </c>
+      <c r="H8" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="16">
+        <v>0.24</v>
+      </c>
+      <c r="J8" s="17">
+        <v>-0.06</v>
+      </c>
+      <c r="K8" s="16">
+        <v>0.33</v>
+      </c>
+      <c r="L8" s="16">
+        <v>0.37</v>
+      </c>
+      <c r="M8" s="16">
+        <v>0.26</v>
+      </c>
+      <c r="N8" s="16">
+        <v>0.27</v>
+      </c>
+      <c r="O8" s="16">
+        <v>0.18</v>
+      </c>
+      <c r="P8" s="17">
+        <v>-0.05</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>0.19</v>
+      </c>
+      <c r="R8" s="16">
+        <v>0.45</v>
+      </c>
+      <c r="S8" s="19">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="11"/>
+      <c r="AA8" s="11"/>
+    </row>
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="C9" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="16">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E9" s="17">
+        <v>-0.01</v>
+      </c>
+      <c r="F9" s="16">
+        <v>0.18</v>
+      </c>
+      <c r="G9" s="16">
+        <v>0.42</v>
+      </c>
+      <c r="H9" s="16">
+        <v>0.19</v>
+      </c>
+      <c r="I9" s="16">
+        <v>0.19</v>
+      </c>
+      <c r="J9" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="K9" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="L9" s="16">
+        <v>0.09</v>
+      </c>
+      <c r="M9" s="16">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N9" s="16">
+        <v>0.33</v>
+      </c>
+      <c r="O9" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="P9" s="16">
+        <v>0.44</v>
+      </c>
+      <c r="Q9" s="16">
+        <v>0.36</v>
+      </c>
+      <c r="R9" s="16">
+        <v>0.37</v>
+      </c>
+      <c r="S9" s="18">
+        <v>2</v>
+      </c>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
+      <c r="V9" s="11"/>
+      <c r="W9" s="11"/>
+      <c r="X9" s="11"/>
+      <c r="Y9" s="11"/>
+      <c r="Z9" s="11"/>
+      <c r="AA9" s="11"/>
+    </row>
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="C10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="16">
+        <v>0.22</v>
+      </c>
+      <c r="E10" s="16">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F10" s="16">
+        <v>0.13</v>
+      </c>
+      <c r="G10" s="17">
+        <v>-0.24</v>
+      </c>
+      <c r="H10" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="I10" s="16">
+        <v>0.27</v>
+      </c>
+      <c r="J10" s="17">
+        <v>-0.27</v>
+      </c>
+      <c r="K10" s="17">
+        <v>-0.02</v>
+      </c>
+      <c r="L10" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="M10" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="N10" s="16">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O10" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="P10" s="16">
+        <v>0.7</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="R10" s="16">
+        <v>0.26</v>
+      </c>
+      <c r="S10" s="18">
+        <v>1.44</v>
+      </c>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="11"/>
+      <c r="AA10" s="11"/>
+    </row>
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="14">
-        <v>45778</v>
-      </c>
-      <c r="I7" s="15" t="s">
+      <c r="C11" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="E11" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="F11" s="16">
+        <v>0.12</v>
+      </c>
+      <c r="G11" s="17">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="H11" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="I11" s="16">
+        <v>0.34</v>
+      </c>
+      <c r="J11" s="16">
+        <v>0.19</v>
+      </c>
+      <c r="K11" s="16">
+        <v>0.49</v>
+      </c>
+      <c r="L11" s="16">
+        <v>0.45</v>
+      </c>
+      <c r="M11" s="16">
+        <v>0.59</v>
+      </c>
+      <c r="N11" s="17">
+        <v>-0.02</v>
+      </c>
+      <c r="O11" s="16">
+        <v>0.41</v>
+      </c>
+      <c r="P11" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="Q11" s="17">
+        <v>-0.1</v>
+      </c>
+      <c r="R11" s="17">
+        <v>-0.1</v>
+      </c>
+      <c r="S11" s="17">
+        <v>-0.24</v>
+      </c>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
+      <c r="AA11" s="11"/>
+    </row>
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9"/>
+      <c r="B12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="C12" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="16">
+        <v>0.73</v>
+      </c>
+      <c r="E12" s="16">
+        <v>0.43</v>
+      </c>
+      <c r="F12" s="16">
+        <v>0.38</v>
+      </c>
+      <c r="G12" s="16">
+        <v>0.93</v>
+      </c>
+      <c r="H12" s="16">
+        <v>0.41</v>
+      </c>
+      <c r="I12" s="16">
+        <v>0.35</v>
+      </c>
+      <c r="J12" s="16">
+        <v>0.52</v>
+      </c>
+      <c r="K12" s="16">
+        <v>0.46</v>
+      </c>
+      <c r="L12" s="16">
+        <v>0.48</v>
+      </c>
+      <c r="M12" s="16">
+        <v>0.47</v>
+      </c>
+      <c r="N12" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="O12" s="17">
+        <v>-0.27</v>
+      </c>
+      <c r="P12" s="16">
+        <v>0.32</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="R12" s="16">
+        <v>0.12</v>
+      </c>
+      <c r="S12" s="16">
+        <v>0.13</v>
+      </c>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="11"/>
+      <c r="W12" s="11"/>
+      <c r="X12" s="11"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="11"/>
+      <c r="AA12" s="11"/>
+    </row>
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="C13" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="16">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E13" s="16">
+        <v>0.61</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G13" s="16">
+        <v>3.16</v>
+      </c>
+      <c r="H13" s="16">
+        <v>1.17</v>
+      </c>
+      <c r="I13" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="J13" s="16">
+        <v>0.64</v>
+      </c>
+      <c r="K13" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="L13" s="16">
+        <v>0.26</v>
+      </c>
+      <c r="M13" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="N13" s="17">
+        <v>-0.05</v>
+      </c>
+      <c r="O13" s="17">
+        <v>-0.04</v>
+      </c>
+      <c r="P13" s="16">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="Q13" s="16">
+        <v>0.19</v>
+      </c>
+      <c r="R13" s="17">
+        <v>-0.06</v>
+      </c>
+      <c r="S13" s="16">
+        <v>0.11</v>
+      </c>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="11"/>
+      <c r="AA13" s="11"/>
+    </row>
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="C14" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="16">
+        <v>0.99</v>
+      </c>
+      <c r="E14" s="16">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="F14" s="16">
+        <v>0.81</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0.95</v>
+      </c>
+      <c r="H14" s="16">
+        <v>0.49</v>
+      </c>
+      <c r="I14" s="16">
+        <v>0.51</v>
+      </c>
+      <c r="J14" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="K14" s="16">
+        <v>0.13</v>
+      </c>
+      <c r="L14" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="M14" s="16">
+        <v>0.17</v>
+      </c>
+      <c r="N14" s="17">
+        <v>-0.1</v>
+      </c>
+      <c r="O14" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="P14" s="17">
+        <v>-0.11</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="R14" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="S14" s="23">
+        <v>-0.05</v>
+      </c>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="11"/>
+      <c r="AA14" s="11"/>
+    </row>
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="N7" s="13" t="s">
+      <c r="C15" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="16">
+        <v>0.51</v>
+      </c>
+      <c r="E15" s="16">
+        <v>0.13</v>
+      </c>
+      <c r="F15" s="16">
+        <v>0.39</v>
+      </c>
+      <c r="G15" s="16">
+        <v>0.21</v>
+      </c>
+      <c r="H15" s="16">
+        <v>0.16</v>
+      </c>
+      <c r="I15" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="J15" s="16">
+        <v>0.18</v>
+      </c>
+      <c r="K15" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="L15" s="17">
+        <v>-0.13</v>
+      </c>
+      <c r="M15" s="17">
+        <v>-0.04</v>
+      </c>
+      <c r="N15" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="O15" s="17">
+        <v>-0.06</v>
+      </c>
+      <c r="P15" s="24">
+        <v>1.21</v>
+      </c>
+      <c r="Q15" s="16">
+        <v>0.19</v>
+      </c>
+      <c r="R15" s="17">
+        <v>-0.1</v>
+      </c>
+      <c r="S15" s="16">
+        <v>0.13</v>
+      </c>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
+      <c r="AA15" s="11"/>
+    </row>
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="C16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="16">
+        <v>0.22</v>
+      </c>
+      <c r="E16" s="17">
+        <v>-0.26</v>
+      </c>
+      <c r="F16" s="16">
+        <v>0.53</v>
+      </c>
+      <c r="G16" s="17">
+        <v>-0.03</v>
+      </c>
+      <c r="H16" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="I16" s="17">
+        <v>-0.05</v>
+      </c>
+      <c r="J16" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="K16" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="L16" s="16">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0.21</v>
+      </c>
+      <c r="N16" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="O16" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="P16" s="17">
+        <v>-0.05</v>
+      </c>
+      <c r="Q16" s="16">
+        <v>0.13</v>
+      </c>
+      <c r="R16" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="S16" s="16">
+        <v>0.31</v>
+      </c>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
+      <c r="AA16" s="11"/>
+    </row>
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="P7" s="13" t="s">
+      <c r="C17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="16">
+        <v>0.33</v>
+      </c>
+      <c r="E17" s="16">
+        <v>0.47</v>
+      </c>
+      <c r="F17" s="16">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G17" s="16">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H17" s="16">
+        <v>1.43</v>
+      </c>
+      <c r="I17" s="16">
+        <v>0.12</v>
+      </c>
+      <c r="J17" s="16">
+        <v>0.24</v>
+      </c>
+      <c r="K17" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="L17" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="M17" s="16">
+        <v>0.19</v>
+      </c>
+      <c r="N17" s="16">
+        <v>0.27</v>
+      </c>
+      <c r="O17" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="P17" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="Q17" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="R17" s="16">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="S17" s="16">
+        <v>0.27</v>
+      </c>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11"/>
+      <c r="X17" s="11"/>
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="11"/>
+      <c r="AA17" s="11"/>
+    </row>
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9"/>
+      <c r="B18" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="Q7" s="13" t="s">
+      <c r="C18" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="E18" s="16">
+        <v>0.49</v>
+      </c>
+      <c r="F18" s="16">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G18" s="16">
+        <v>0.78</v>
+      </c>
+      <c r="H18" s="16">
+        <v>2.74</v>
+      </c>
+      <c r="I18" s="16">
+        <v>0.72</v>
+      </c>
+      <c r="J18" s="16">
+        <v>0.27</v>
+      </c>
+      <c r="K18" s="16">
+        <v>0.65</v>
+      </c>
+      <c r="L18" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="N18" s="16">
+        <v>0.26</v>
+      </c>
+      <c r="O18" s="16">
+        <v>0.45</v>
+      </c>
+      <c r="P18" s="16">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Q18" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="R18" s="16">
+        <v>0.37</v>
+      </c>
+      <c r="S18" s="16">
+        <v>0.33</v>
+      </c>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11"/>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
+      <c r="AA18" s="11"/>
+    </row>
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9"/>
+      <c r="B19" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="R7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="S7" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="T7" s="17"/>
-      <c r="U7" s="17"/>
-      <c r="V7" s="17"/>
-      <c r="W7" s="17"/>
-      <c r="X7" s="17"/>
-      <c r="Y7" s="17"/>
-      <c r="Z7" s="17"/>
-      <c r="AA7" s="17"/>
-    </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
-      <c r="B8" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="18" t="s">
+      <c r="C19" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="N8" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="O8" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="P8" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="R8" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S8" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="T8" s="17"/>
-      <c r="U8" s="17"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="17"/>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="17"/>
-    </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q9" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="R9" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="S9" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="T9" s="17"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="17"/>
-    </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="L10" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="M10" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="N10" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="O10" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="P10" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q10" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="R10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="S10" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="T10" s="17"/>
-      <c r="U10" s="17"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="17"/>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="17"/>
-    </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="N11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="P11" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q11" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="R11" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="S11" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="T11" s="17"/>
-      <c r="U11" s="17"/>
-      <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="17"/>
-      <c r="AA11" s="17"/>
-    </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="K12" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12" s="19" t="s">
+      <c r="D19" s="20">
+        <v>6.21</v>
+      </c>
+      <c r="E19" s="20">
+        <v>3.97</v>
+      </c>
+      <c r="F19" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="G19" s="20">
         <v>8</v>
       </c>
-      <c r="M12" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="N12" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="O12" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="P12" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q12" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="R12" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="S12" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="17"/>
-      <c r="AA12" s="17"/>
-    </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="21">
-        <v>45992</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="N13" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="O13" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="P13" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q13" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="R13" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="S13" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="T13" s="17"/>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="17"/>
-      <c r="Y13" s="17"/>
-      <c r="Z13" s="17"/>
-      <c r="AA13" s="17"/>
-    </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="K14" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="L14" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="M14" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="N14" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="O14" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="P14" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q14" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="R14" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="S14" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="T14" s="17"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
-      <c r="X14" s="17"/>
-      <c r="Y14" s="17"/>
-      <c r="Z14" s="17"/>
-      <c r="AA14" s="17"/>
-    </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L15" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="M15" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="O15" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="P15" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q15" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="R15" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="S15" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="T15" s="17"/>
-      <c r="U15" s="17"/>
-      <c r="V15" s="17"/>
-      <c r="W15" s="17"/>
-      <c r="X15" s="17"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="17"/>
-      <c r="AA15" s="17"/>
-    </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="K16" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="L16" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="M16" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="N16" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="O16" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="P16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q16" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="R16" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="S16" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="T16" s="17"/>
-      <c r="U16" s="17"/>
-      <c r="V16" s="17"/>
-      <c r="W16" s="17"/>
-      <c r="X16" s="17"/>
-      <c r="Y16" s="17"/>
-      <c r="Z16" s="17"/>
-      <c r="AA16" s="17"/>
-    </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="I17" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="K17" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="L17" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="M17" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="N17" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="O17" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="P17" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q17" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="R17" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="S17" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="T17" s="17"/>
-      <c r="U17" s="17"/>
-      <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
-      <c r="X17" s="17"/>
-      <c r="Y17" s="17"/>
-      <c r="Z17" s="17"/>
-      <c r="AA17" s="17"/>
-    </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
-      <c r="B18" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="I18" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J18" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="K18" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="M18" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="N18" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="O18" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="P18" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q18" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="R18" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="S18" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="T18" s="17"/>
-      <c r="U18" s="17"/>
-      <c r="V18" s="17"/>
-      <c r="W18" s="17"/>
-      <c r="X18" s="17"/>
-      <c r="Y18" s="17"/>
-      <c r="Z18" s="17"/>
-      <c r="AA18" s="17"/>
-    </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="G19" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="H19" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="J19" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="K19" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="L19" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="M19" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="N19" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="O19" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="P19" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q19" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="R19" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="S19" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
-      <c r="X19" s="17"/>
-      <c r="Y19" s="17"/>
-      <c r="Z19" s="17"/>
-      <c r="AA19" s="17"/>
+      <c r="H19" s="20">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="I19" s="20">
+        <v>3.3</v>
+      </c>
+      <c r="J19" s="20">
+        <v>2.37</v>
+      </c>
+      <c r="K19" s="20">
+        <v>3.72</v>
+      </c>
+      <c r="L19" s="20">
+        <v>3.27</v>
+      </c>
+      <c r="M19" s="20">
+        <v>3.23</v>
+      </c>
+      <c r="N19" s="20">
+        <v>1.59</v>
+      </c>
+      <c r="O19" s="20">
+        <v>1.53</v>
+      </c>
+      <c r="P19" s="20">
+        <v>4.21</v>
+      </c>
+      <c r="Q19" s="20">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="R19" s="20">
+        <v>1.48</v>
+      </c>
+      <c r="S19" s="20">
+        <v>2.63</v>
+      </c>
+      <c r="T19" s="11"/>
+      <c r="U19" s="11"/>
+      <c r="V19" s="11"/>
+      <c r="W19" s="11"/>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="11"/>
+      <c r="Z19" s="11"/>
+      <c r="AA19" s="11"/>
     </row>
     <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -2355,23 +2028,7 @@
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
+      <c r="S32" s="21"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
@@ -2384,23 +2041,7 @@
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
+      <c r="S33" s="21"/>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
@@ -2413,23 +2054,7 @@
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
+      <c r="S34" s="21"/>
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
@@ -2442,23 +2067,7 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
+      <c r="S35" s="21"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
@@ -2471,23 +2080,6 @@
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
@@ -2500,23 +2092,6 @@
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
@@ -2529,23 +2104,6 @@
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
@@ -2558,23 +2116,6 @@
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
@@ -2587,23 +2128,6 @@
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
-      <c r="R40" s="1"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
@@ -2616,23 +2140,6 @@
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
@@ -2645,23 +2152,6 @@
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
@@ -2674,23 +2164,6 @@
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
@@ -2703,23 +2176,6 @@
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
@@ -7836,786 +7292,787 @@
     <row r="222" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="223" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="224" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="8" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>